--- a/public/downloads/estimate-slab-d9b2e5.xlsx
+++ b/public/downloads/estimate-slab-d9b2e5.xlsx
@@ -6,13 +6,15 @@
   <sheets>
     <sheet sheetId="1" name="📋 How to Use" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Estimate" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="📝 Change Orders" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="📍 Site Conditions" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="249">
   <si>
     <t>📋 HOW TO USE: Concrete Slab Estimate</t>
   </si>
@@ -95,6 +97,24 @@
     <t>✏️ EDITABLE CELLS: Yellow cells: quantities, unit prices, hours, rates, client info, overhead %, profit %</t>
   </si>
   <si>
+    <t>💡 PRO TIPS — INSIDER KNOWLEDGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  💡 Always install vapor barrier under enclosed slabs — moisture wicking through concrete ruins future floor coatings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  💡 Control joints must be cut within 6-12 hours. Cut depth = 1/4 of slab thickness. Waiting too long = random cracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  💡 For garage slabs, pour 1-2" above the driveway apron — prevents water from flowing into the garage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  💡 If the client plans walls later, install anchor bolts DURING the pour. Coming back to drill and epoxy costs 3x more</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  💡 Thickened edges add only $2-3/LF but increase structural integrity dramatically — always recommend them</t>
+  </si>
+  <si>
     <t>TIPS FOR PRINTING / PDF EXPORT</t>
   </si>
   <si>
@@ -492,6 +512,255 @@
   </si>
   <si>
     <t>Template from EstimateConcrete.com — Free concrete contractor tools</t>
+  </si>
+  <si>
+    <t>📝 CHANGE ORDER LOG</t>
+  </si>
+  <si>
+    <t>Track all scope changes, approvals, and cost impacts. Every change must be documented before work begins.</t>
+  </si>
+  <si>
+    <t>Project:</t>
+  </si>
+  <si>
+    <t>Original Contract $:</t>
+  </si>
+  <si>
+    <t>Client:</t>
+  </si>
+  <si>
+    <t>CO #</t>
+  </si>
+  <si>
+    <t>Description of Change</t>
+  </si>
+  <si>
+    <t>Added Cost</t>
+  </si>
+  <si>
+    <t>Approval Date</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Running Total</t>
+  </si>
+  <si>
+    <t>TOTAL CHANGE ORDERS</t>
+  </si>
+  <si>
+    <t>ORIGINAL CONTRACT AMOUNT</t>
+  </si>
+  <si>
+    <t>REVISED CONTRACT TOTAL</t>
+  </si>
+  <si>
+    <t>SUMMARY BY STATUS</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Rejected</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>📍 SITE CONDITIONS ASSESSMENT</t>
+  </si>
+  <si>
+    <t>Complete during site visit. Accurate assessment prevents costly surprises on pour day.</t>
+  </si>
+  <si>
+    <t>Site Visit Date:</t>
+  </si>
+  <si>
+    <t>Assessed By:</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Condition / Check Item</t>
+  </si>
+  <si>
+    <t>Notes / Details</t>
+  </si>
+  <si>
+    <t>Photo Ref #</t>
+  </si>
+  <si>
+    <t>Action Needed</t>
+  </si>
+  <si>
+    <t>Truck access width (min 10' wide, 13' overhead)</t>
+  </si>
+  <si>
+    <t>Ground conditions — can trucks drive on site?</t>
+  </si>
+  <si>
+    <t>Underground utilities located and marked (call 811)</t>
+  </si>
+  <si>
+    <t>Water source available on site</t>
+  </si>
+  <si>
+    <t>Existing structures/surfaces to protect</t>
+  </si>
+  <si>
+    <t>Drainage pattern — where does water flow?</t>
+  </si>
+  <si>
+    <t>Soil type (clay / sand / rock / fill)</t>
+  </si>
+  <si>
+    <t>Grade / slope measurements taken</t>
+  </si>
+  <si>
+    <t>Property line / setback distances confirmed</t>
+  </si>
+  <si>
+    <t>Permits required (check local code office)</t>
+  </si>
+  <si>
+    <t>Access width for concrete truck (min 10')</t>
+  </si>
+  <si>
+    <t>Existing slab removal needed (Y/N)</t>
+  </si>
+  <si>
+    <t>Soil bearing capacity (compaction test done?)</t>
+  </si>
+  <si>
+    <t>Water table depth</t>
+  </si>
+  <si>
+    <t>Slope of site — fill needed?</t>
+  </si>
+  <si>
+    <t>Underground utilities marked</t>
+  </si>
+  <si>
+    <t>Intended use (garage, shop, storage, equipment)</t>
+  </si>
+  <si>
+    <t>Future wall or building placement on slab</t>
+  </si>
+  <si>
+    <t>📸 SITE PHOTO LOG</t>
+  </si>
+  <si>
+    <t>Photo #</t>
+  </si>
+  <si>
+    <t>Description / Location</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>File Name</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Overall site — wide angle</t>
+  </si>
+  <si>
+    <t>Before condition</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Truck access point</t>
+  </si>
+  <si>
+    <t>Access verification</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Work area — existing surface</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Drainage / water flow</t>
+  </si>
+  <si>
+    <t>Drainage planning</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Adjacent structures</t>
+  </si>
+  <si>
+    <t>Protection planning</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Utility markings</t>
+  </si>
+  <si>
+    <t>Utility locations</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Soil condition</t>
+  </si>
+  <si>
+    <t>Soil assessment</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Grade / slope</t>
+  </si>
+  <si>
+    <t>Grading reference</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Property boundaries</t>
+  </si>
+  <si>
+    <t>Permit reference</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Obstacles / challenges</t>
+  </si>
+  <si>
+    <t>Planning</t>
+  </si>
+  <si>
+    <t>OVERALL SITE ASSESSMENT:</t>
   </si>
 </sst>
 </file>
@@ -501,7 +770,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -591,8 +860,17 @@
       <color rgb="FF94A3B8"/>
       <sz val="8"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF94A3B8"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -602,6 +880,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -647,7 +930,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -660,6 +943,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -670,28 +954,44 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1034,7 +1334,7 @@
   <sheetPr>
     <tabColor rgb="FFFEF3C7"/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1164,46 +1464,46 @@
       <c r="B20" s="7"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+      <c r="B22" s="8"/>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="8"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+      <c r="B23" s="3"/>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="8"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+      <c r="B24" s="3"/>
+    </row>
+    <row r="25" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="8"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+      <c r="B25" s="3"/>
+    </row>
+    <row r="26" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="8"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="8"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+      <c r="B27" s="3"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="8"/>
+      <c r="B29" s="2"/>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
@@ -1212,13 +1512,49 @@
       <c r="B30" s="9"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="10"/>
+      <c r="B31" s="9"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="9"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="9"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="9"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="9"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="10"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="22">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
@@ -1232,9 +1568,15 @@
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1255,1125 +1597,1125 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="A1" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
+      <c r="A2" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
     </row>
     <row r="3" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
+      <c r="A3" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>39</v>
+      <c r="A4" s="14" t="s">
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>41</v>
+        <v>46</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>43</v>
+      <c r="A6" s="15" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="15" t="s">
+      <c r="A7" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="21">
+        <v>12</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="22">
+        <v>150</v>
+      </c>
+      <c r="E14" s="23">
+        <f>B14*D14</f>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="21">
+        <v>8</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="22">
+        <v>35</v>
+      </c>
+      <c r="E15" s="23">
+        <f>B15*D15</f>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="21">
+        <v>1200</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="22">
+        <v>0.15</v>
+      </c>
+      <c r="E16" s="23">
+        <f>B16*D16</f>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="21">
+        <v>400</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="22">
+        <v>0.75</v>
+      </c>
+      <c r="E17" s="23">
+        <f>B17*D17</f>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="21">
+        <v>1200</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="22">
+        <v>0.45</v>
+      </c>
+      <c r="E18" s="23">
+        <f>B18*D18</f>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="21">
+        <v>120</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="22">
+        <v>1.25</v>
+      </c>
+      <c r="E19" s="23">
+        <f>B19*D19</f>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="21">
+        <v>5</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="22">
+        <v>18</v>
+      </c>
+      <c r="E20" s="23">
+        <f>B20*D20</f>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="21">
+        <v>1</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="22">
+        <v>350</v>
+      </c>
+      <c r="E21" s="23">
+        <f>B21*D21</f>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="24">
+        <f>SUM(E14:E21)</f>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="21">
+        <v>16</v>
+      </c>
+      <c r="C26" s="20"/>
+      <c r="D26" s="22">
+        <v>55</v>
+      </c>
+      <c r="E26" s="23">
+        <f>B26*D26</f>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="21">
+        <v>12</v>
+      </c>
+      <c r="C27" s="20"/>
+      <c r="D27" s="22">
+        <v>55</v>
+      </c>
+      <c r="E27" s="23">
+        <f>B27*D27</f>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="21">
+        <v>8</v>
+      </c>
+      <c r="C28" s="20"/>
+      <c r="D28" s="22">
+        <v>50</v>
+      </c>
+      <c r="E28" s="23">
+        <f>B28*D28</f>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="21">
+        <v>4</v>
+      </c>
+      <c r="C29" s="20"/>
+      <c r="D29" s="22">
         <v>45</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="17" t="s">
+      <c r="E29" s="23">
+        <f>B29*D29</f>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="21">
+        <v>8</v>
+      </c>
+      <c r="C30" s="20"/>
+      <c r="D30" s="22">
         <v>55</v>
       </c>
-      <c r="E12" s="17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="18" t="s">
+      <c r="E30" s="23">
+        <f>B30*D30</f>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="21">
+        <v>16</v>
+      </c>
+      <c r="C31" s="20"/>
+      <c r="D31" s="22">
+        <v>65</v>
+      </c>
+      <c r="E31" s="23">
+        <f>B31*D31</f>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B32" s="21">
+        <v>4</v>
+      </c>
+      <c r="C32" s="20"/>
+      <c r="D32" s="22">
         <v>55</v>
       </c>
-      <c r="E13" s="18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="20">
-        <v>12</v>
-      </c>
-      <c r="C14" s="19" t="s">
+      <c r="E32" s="23">
+        <f>B32*D32</f>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="21">
+        <v>6</v>
+      </c>
+      <c r="C33" s="20"/>
+      <c r="D33" s="22">
+        <v>45</v>
+      </c>
+      <c r="E33" s="23">
+        <f>B33*D33</f>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="24">
+        <f>SUM(E26:E33)</f>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="21">
+      <c r="C36" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B38" s="21">
+        <v>1</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D38" s="22">
+        <v>350</v>
+      </c>
+      <c r="E38" s="23">
+        <f>B38*D38</f>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" s="21">
+        <v>1</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D39" s="22">
+        <v>125</v>
+      </c>
+      <c r="E39" s="23">
+        <f>B39*D39</f>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B40" s="21">
+        <v>1</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D40" s="22">
+        <v>85</v>
+      </c>
+      <c r="E40" s="23">
+        <f>B40*D40</f>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" s="21">
+        <v>1</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D41" s="22">
         <v>150</v>
       </c>
-      <c r="E14" s="22">
-        <f>B14*D14</f>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="20">
-        <v>8</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="21">
-        <v>35</v>
-      </c>
-      <c r="E15" s="22">
-        <f>B15*D15</f>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B16" s="20">
-        <v>1200</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" s="21">
+      <c r="E41" s="23">
+        <f>B41*D41</f>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B42" s="21">
+        <v>1</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D42" s="22">
+        <v>125</v>
+      </c>
+      <c r="E42" s="23">
+        <f>B42*D42</f>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B43" s="21">
+        <v>1</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D43" s="22">
+        <v>250</v>
+      </c>
+      <c r="E43" s="23">
+        <f>B43*D43</f>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="24">
+        <f>SUM(E38:E43)</f>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B47" s="21"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="23">
+        <f>B47*D47</f>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" s="21"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="23">
+        <f>B48*D48</f>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B49" s="21"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="23">
+        <f>B49*D49</f>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B50" s="21"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="23">
+        <f>B50*D50</f>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B51" s="21"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="23">
+        <f>B51*D51</f>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B52" s="21"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="23">
+        <f>B52*D52</f>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B53" s="21"/>
+      <c r="C53" s="20"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="23">
+        <f>B53*D53</f>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="B54" s="21"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="23">
+        <f>B54*D54</f>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B55" s="19"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="24">
+        <f>SUM(E47:E54)</f>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" s="20"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="23">
+        <f>E22</f>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B59" s="20"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="23">
+        <f>E34</f>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B60" s="20"/>
+      <c r="C60" s="20"/>
+      <c r="D60" s="20"/>
+      <c r="E60" s="23">
+        <f>E44</f>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B61" s="20"/>
+      <c r="C61" s="20"/>
+      <c r="D61" s="20"/>
+      <c r="E61" s="23">
+        <f>E55</f>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="B62" s="19"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="24">
+        <f>E58+E59+E60+E61</f>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="B63" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="C63" s="20"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="23">
+        <f>E62*B63</f>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="B64" s="26">
         <v>0.15</v>
       </c>
-      <c r="E16" s="22">
-        <f>B16*D16</f>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="20">
-        <v>400</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" s="21">
-        <v>0.75</v>
-      </c>
-      <c r="E17" s="22">
-        <f>B17*D17</f>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="B18" s="20">
-        <v>1200</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D18" s="21">
-        <v>0.45</v>
-      </c>
-      <c r="E18" s="22">
-        <f>B18*D18</f>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19" s="20">
-        <v>120</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" s="21">
-        <v>1.25</v>
-      </c>
-      <c r="E19" s="22">
-        <f>B19*D19</f>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="B20" s="20">
-        <v>5</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="21">
-        <v>18</v>
-      </c>
-      <c r="E20" s="22">
-        <f>B20*D20</f>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" s="20">
-        <v>1</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" s="21">
-        <v>350</v>
-      </c>
-      <c r="E21" s="22">
-        <f>B21*D21</f>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="23">
-        <f>SUM(E14:E21)</f>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26" s="20">
-        <v>16</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="21">
-        <v>55</v>
-      </c>
-      <c r="E26" s="22">
-        <f>B26*D26</f>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="B27" s="20">
-        <v>12</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="21">
-        <v>55</v>
-      </c>
-      <c r="E27" s="22">
-        <f>B27*D27</f>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="B28" s="20">
-        <v>8</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="21">
-        <v>50</v>
-      </c>
-      <c r="E28" s="22">
-        <f>B28*D28</f>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="B29" s="20">
-        <v>4</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="21">
-        <v>45</v>
-      </c>
-      <c r="E29" s="22">
-        <f>B29*D29</f>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="B30" s="20">
-        <v>8</v>
-      </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="21">
-        <v>55</v>
-      </c>
-      <c r="E30" s="22">
-        <f>B30*D30</f>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="B31" s="20">
-        <v>16</v>
-      </c>
-      <c r="C31" s="19"/>
-      <c r="D31" s="21">
-        <v>65</v>
-      </c>
-      <c r="E31" s="22">
-        <f>B31*D31</f>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="B32" s="20">
-        <v>4</v>
-      </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="21">
-        <v>55</v>
-      </c>
-      <c r="E32" s="22">
-        <f>B32*D32</f>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="B33" s="20">
-        <v>6</v>
-      </c>
-      <c r="C33" s="19"/>
-      <c r="D33" s="21">
-        <v>45</v>
-      </c>
-      <c r="E33" s="22">
-        <f>B33*D33</f>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="23">
-        <f>SUM(E26:E33)</f>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="B38" s="20">
-        <v>1</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D38" s="21">
-        <v>350</v>
-      </c>
-      <c r="E38" s="22">
-        <f>B38*D38</f>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="B39" s="20">
-        <v>1</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D39" s="21">
+      <c r="C64" s="20"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="23">
+        <f>(E62+E63)*B64</f>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="B65" s="28"/>
+      <c r="C65" s="28"/>
+      <c r="D65" s="28"/>
+      <c r="E65" s="29">
+        <f>E62+E63+E64</f>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="18"/>
+      <c r="E67" s="18"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="B68" s="21"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="B69" s="21"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="E39" s="22">
-        <f>B39*D39</f>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="B40" s="20">
-        <v>1</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D40" s="21">
-        <v>85</v>
-      </c>
-      <c r="E40" s="22">
-        <f>B40*D40</f>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="B41" s="20">
-        <v>1</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D41" s="21">
+      <c r="B70" s="21"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="B71" s="21"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="B72" s="21"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="B73" s="21"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="B74" s="21"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="B75" s="21"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="21"/>
+    </row>
+    <row r="77" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B77" s="18"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="18"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="B78" s="31"/>
+      <c r="C78" s="31"/>
+      <c r="D78" s="31"/>
+      <c r="E78" s="31"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="B79" s="31"/>
+      <c r="C79" s="31"/>
+      <c r="D79" s="31"/>
+      <c r="E79" s="31"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="B80" s="31"/>
+      <c r="C80" s="31"/>
+      <c r="D80" s="31"/>
+      <c r="E80" s="31"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="B81" s="31"/>
+      <c r="C81" s="31"/>
+      <c r="D81" s="31"/>
+      <c r="E81" s="31"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="B82" s="31"/>
+      <c r="C82" s="31"/>
+      <c r="D82" s="31"/>
+      <c r="E82" s="31"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="B83" s="31"/>
+      <c r="C83" s="31"/>
+      <c r="D83" s="31"/>
+      <c r="E83" s="31"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="B84" s="31"/>
+      <c r="C84" s="31"/>
+      <c r="D84" s="31"/>
+      <c r="E84" s="31"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="B85" s="31"/>
+      <c r="C85" s="31"/>
+      <c r="D85" s="31"/>
+      <c r="E85" s="31"/>
+    </row>
+    <row r="87" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="B87" s="18"/>
+      <c r="C87" s="18"/>
+      <c r="D87" s="18"/>
+      <c r="E87" s="18"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="B88" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C88" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="D88" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="E88" s="19" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="21"/>
+      <c r="B89" s="21"/>
+      <c r="C89" s="20"/>
+      <c r="D89" s="22"/>
+      <c r="E89" s="21"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="21"/>
+      <c r="B90" s="21"/>
+      <c r="C90" s="20"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="21"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="21"/>
+      <c r="B91" s="21"/>
+      <c r="C91" s="20"/>
+      <c r="D91" s="22"/>
+      <c r="E91" s="21"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="21"/>
+      <c r="B92" s="21"/>
+      <c r="C92" s="20"/>
+      <c r="D92" s="22"/>
+      <c r="E92" s="21"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="21"/>
+      <c r="B93" s="21"/>
+      <c r="C93" s="20"/>
+      <c r="D93" s="22"/>
+      <c r="E93" s="21"/>
+    </row>
+    <row r="95" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="B95" s="18"/>
+      <c r="C95" s="18"/>
+      <c r="D95" s="18"/>
+      <c r="E95" s="18"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B96" s="32"/>
+      <c r="C96" s="32"/>
+      <c r="D96" s="32"/>
+      <c r="E96" s="32"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="B97" s="32"/>
+      <c r="C97" s="32"/>
+      <c r="D97" s="32"/>
+      <c r="E97" s="32"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="B98" s="32"/>
+      <c r="C98" s="32"/>
+      <c r="D98" s="32"/>
+      <c r="E98" s="32"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="E41" s="22">
-        <f>B41*D41</f>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="B42" s="20">
-        <v>1</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D42" s="21">
-        <v>125</v>
-      </c>
-      <c r="E42" s="22">
-        <f>B42*D42</f>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="B43" s="20">
-        <v>1</v>
-      </c>
-      <c r="C43" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D43" s="21">
-        <v>250</v>
-      </c>
-      <c r="E43" s="22">
-        <f>B43*D43</f>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="B44" s="18"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="23">
-        <f>SUM(E38:E43)</f>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="B47" s="20"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="22">
-        <f>B47*D47</f>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="B48" s="20"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="22">
-        <f>B48*D48</f>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="B49" s="20"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="22">
-        <f>B49*D49</f>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B50" s="20"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="22">
-        <f>B50*D50</f>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="B51" s="20"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="22">
-        <f>B51*D51</f>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="B52" s="20"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="22">
-        <f>B52*D52</f>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="B53" s="20"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="22">
-        <f>B53*D53</f>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="B54" s="20"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="22">
-        <f>B54*D54</f>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="23">
-        <f>SUM(E47:E54)</f>
-      </c>
-    </row>
-    <row r="57" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="22">
-        <f>E22</f>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="22">
-        <f>E34</f>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="22">
-        <f>E44</f>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="B61" s="19"/>
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="22">
-        <f>E55</f>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="B62" s="18"/>
-      <c r="C62" s="18"/>
-      <c r="D62" s="18"/>
-      <c r="E62" s="23">
-        <f>E58+E59+E60+E61</f>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B63" s="25">
-        <v>0.1</v>
-      </c>
-      <c r="C63" s="19"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="22">
-        <f>E62*B63</f>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="B64" s="25">
-        <v>0.15</v>
-      </c>
-      <c r="C64" s="19"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="22">
-        <f>(E62+E63)*B64</f>
-      </c>
-    </row>
-    <row r="65" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="B65" s="27"/>
-      <c r="C65" s="27"/>
-      <c r="D65" s="27"/>
-      <c r="E65" s="28">
-        <f>E62+E63+E64</f>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="B67" s="17"/>
-      <c r="C67" s="17"/>
-      <c r="D67" s="17"/>
-      <c r="E67" s="17"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="B68" s="20"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="20"/>
-      <c r="E68" s="20"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="B69" s="20"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="29" t="s">
-        <v>120</v>
-      </c>
-      <c r="B71" s="20"/>
-      <c r="C71" s="20"/>
-      <c r="D71" s="20"/>
-      <c r="E71" s="20"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="B72" s="20"/>
-      <c r="C72" s="20"/>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="29" t="s">
-        <v>122</v>
-      </c>
-      <c r="B73" s="20"/>
-      <c r="C73" s="20"/>
-      <c r="D73" s="20"/>
-      <c r="E73" s="20"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="B74" s="20"/>
-      <c r="C74" s="20"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-    </row>
-    <row r="77" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B77" s="17"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="17"/>
-      <c r="E77" s="17"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="B78" s="30"/>
-      <c r="C78" s="30"/>
-      <c r="D78" s="30"/>
-      <c r="E78" s="30"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="B79" s="30"/>
-      <c r="C79" s="30"/>
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="B80" s="30"/>
-      <c r="C80" s="30"/>
-      <c r="D80" s="30"/>
-      <c r="E80" s="30"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="B81" s="30"/>
-      <c r="C81" s="30"/>
-      <c r="D81" s="30"/>
-      <c r="E81" s="30"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="B82" s="30"/>
-      <c r="C82" s="30"/>
-      <c r="D82" s="30"/>
-      <c r="E82" s="30"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="B83" s="30"/>
-      <c r="C83" s="30"/>
-      <c r="D83" s="30"/>
-      <c r="E83" s="30"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="B84" s="30"/>
-      <c r="C84" s="30"/>
-      <c r="D84" s="30"/>
-      <c r="E84" s="30"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="B85" s="30"/>
-      <c r="C85" s="30"/>
-      <c r="D85" s="30"/>
-      <c r="E85" s="30"/>
-    </row>
-    <row r="87" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="B87" s="17"/>
-      <c r="C87" s="17"/>
-      <c r="D87" s="17"/>
-      <c r="E87" s="17"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="B88" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C88" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="D88" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="E88" s="18" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="20"/>
-      <c r="B89" s="20"/>
-      <c r="C89" s="19"/>
-      <c r="D89" s="21"/>
-      <c r="E89" s="20"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="20"/>
-      <c r="B90" s="20"/>
-      <c r="C90" s="19"/>
-      <c r="D90" s="21"/>
-      <c r="E90" s="20"/>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="20"/>
-      <c r="B91" s="20"/>
-      <c r="C91" s="19"/>
-      <c r="D91" s="21"/>
-      <c r="E91" s="20"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="20"/>
-      <c r="B92" s="20"/>
-      <c r="C92" s="19"/>
-      <c r="D92" s="21"/>
-      <c r="E92" s="20"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="20"/>
-      <c r="B93" s="20"/>
-      <c r="C93" s="19"/>
-      <c r="D93" s="21"/>
-      <c r="E93" s="20"/>
-    </row>
-    <row r="95" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="B95" s="17"/>
-      <c r="C95" s="17"/>
-      <c r="D95" s="17"/>
-      <c r="E95" s="17"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="B96" s="31"/>
-      <c r="C96" s="31"/>
-      <c r="D96" s="31"/>
-      <c r="E96" s="31"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="B97" s="31"/>
-      <c r="C97" s="31"/>
-      <c r="D97" s="31"/>
-      <c r="E97" s="31"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="B98" s="31"/>
-      <c r="C98" s="31"/>
-      <c r="D98" s="31"/>
-      <c r="E98" s="31"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="B99" s="31"/>
-      <c r="C99" s="31"/>
-      <c r="D99" s="31"/>
-      <c r="E99" s="31"/>
+      <c r="B99" s="32"/>
+      <c r="C99" s="32"/>
+      <c r="D99" s="32"/>
+      <c r="E99" s="32"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="B100" s="31"/>
-      <c r="C100" s="31"/>
-      <c r="D100" s="31"/>
-      <c r="E100" s="31"/>
+      <c r="A100" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="B100" s="32"/>
+      <c r="C100" s="32"/>
+      <c r="D100" s="32"/>
+      <c r="E100" s="32"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="B101" s="31"/>
-      <c r="C101" s="31"/>
-      <c r="D101" s="31"/>
-      <c r="E101" s="31"/>
+      <c r="A101" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="B101" s="32"/>
+      <c r="C101" s="32"/>
+      <c r="D101" s="32"/>
+      <c r="E101" s="32"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="B102" s="31"/>
-      <c r="C102" s="31"/>
-      <c r="D102" s="31"/>
-      <c r="E102" s="31"/>
+      <c r="A102" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="B102" s="32"/>
+      <c r="C102" s="32"/>
+      <c r="D102" s="32"/>
+      <c r="E102" s="32"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="B103" s="31"/>
-      <c r="C103" s="31"/>
-      <c r="D103" s="31"/>
-      <c r="E103" s="31"/>
+      <c r="A103" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="B103" s="32"/>
+      <c r="C103" s="32"/>
+      <c r="D103" s="32"/>
+      <c r="E103" s="32"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="B104" s="31"/>
-      <c r="C104" s="31"/>
-      <c r="D104" s="31"/>
-      <c r="E104" s="31"/>
+      <c r="A104" s="32" t="s">
+        <v>155</v>
+      </c>
+      <c r="B104" s="32"/>
+      <c r="C104" s="32"/>
+      <c r="D104" s="32"/>
+      <c r="E104" s="32"/>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="32" t="s">
-        <v>150</v>
+      <c r="A106" s="33" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="13" t="s">
-        <v>154</v>
+      <c r="A111" s="14" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B112"/>
       <c r="C112"/>
@@ -2382,7 +2724,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B113"/>
       <c r="C113"/>
@@ -2391,17 +2733,17 @@
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="33" t="s">
-        <v>159</v>
+      <c r="A118" s="34" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -2450,4 +2792,957 @@
     <oddFooter>EstimateConcrete.com — Professional Concrete Estimating Tools</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFEF4444"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="21"/>
+      <c r="D4" s="35" t="s">
+        <v>169</v>
+      </c>
+      <c r="E4" s="22"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="35" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="21"/>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="36">
+        <v>1</v>
+      </c>
+      <c r="B8" s="21"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="23">
+        <f>IF(C8="","",SUM(C$8:C8))</f>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="36">
+        <v>2</v>
+      </c>
+      <c r="B9" s="21"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="23">
+        <f>IF(C9="","",SUM(C$8:C9))</f>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="36">
+        <v>3</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="23">
+        <f>IF(C10="","",SUM(C$8:C10))</f>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="36">
+        <v>4</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="23">
+        <f>IF(C11="","",SUM(C$8:C11))</f>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="36">
+        <v>5</v>
+      </c>
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="23">
+        <f>IF(C12="","",SUM(C$8:C12))</f>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="36">
+        <v>6</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="23">
+        <f>IF(C13="","",SUM(C$8:C13))</f>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="36">
+        <v>7</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="23">
+        <f>IF(C14="","",SUM(C$8:C14))</f>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="36">
+        <v>8</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="23">
+        <f>IF(C15="","",SUM(C$8:C15))</f>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="36">
+        <v>9</v>
+      </c>
+      <c r="B16" s="21"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="23">
+        <f>IF(C16="","",SUM(C$8:C16))</f>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="36">
+        <v>10</v>
+      </c>
+      <c r="B17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="23">
+        <f>IF(C17="","",SUM(C$8:C17))</f>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="36">
+        <v>11</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="23">
+        <f>IF(C18="","",SUM(C$8:C18))</f>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="36">
+        <v>12</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="23">
+        <f>IF(C19="","",SUM(C$8:C19))</f>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="36">
+        <v>13</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="23">
+        <f>IF(C20="","",SUM(C$8:C20))</f>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="36">
+        <v>14</v>
+      </c>
+      <c r="B21" s="21"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="23">
+        <f>IF(C21="","",SUM(C$8:C21))</f>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="36">
+        <v>15</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="23">
+        <f>IF(C22="","",SUM(C$8:C22))</f>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="37"/>
+      <c r="B24" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="C24" s="39">
+        <f>SUM(C8:C22)</f>
+      </c>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="20"/>
+      <c r="B25" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="C25" s="23">
+        <f>E4</f>
+      </c>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+    </row>
+    <row r="26" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="28"/>
+      <c r="B26" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="C26" s="29">
+        <f>E4+C24</f>
+      </c>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="40" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" s="20">
+        <f>COUNTIF(F8:F22,"Pending")</f>
+      </c>
+      <c r="D29" s="23">
+        <f>SUMIFS(C8:C22,F8:F22,"Pending")</f>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="C30" s="20">
+        <f>COUNTIF(F8:F22,"Approved")</f>
+      </c>
+      <c r="D30" s="23">
+        <f>SUMIFS(C8:C22,F8:F22,"Approved")</f>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C31" s="20">
+        <f>COUNTIF(F8:F22,"Rejected")</f>
+      </c>
+      <c r="D31" s="23">
+        <f>SUMIFS(C8:C22,F8:F22,"Rejected")</f>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C32" s="20">
+        <f>COUNTIF(F8:F22,"Completed")</f>
+      </c>
+      <c r="D32" s="23">
+        <f>SUMIFS(C8:C22,F8:F22,"Completed")</f>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" sqref="F10:F22">
+      <formula1>"Pending,Approved,Rejected,Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F8:F22">
+      <formula1>"Pending,Approved,Rejected,Completed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF3B82F6"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F48"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="B5" s="21"/>
+      <c r="C5" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="D5" s="21"/>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="36">
+        <v>1</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="36">
+        <v>2</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="36">
+        <v>3</v>
+      </c>
+      <c r="B10" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="36">
+        <v>4</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="36">
+        <v>5</v>
+      </c>
+      <c r="B12" s="41" t="s">
+        <v>199</v>
+      </c>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="36">
+        <v>6</v>
+      </c>
+      <c r="B13" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="36">
+        <v>7</v>
+      </c>
+      <c r="B14" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="36">
+        <v>8</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="36">
+        <v>9</v>
+      </c>
+      <c r="B16" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="36">
+        <v>10</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>204</v>
+      </c>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="36">
+        <v>11</v>
+      </c>
+      <c r="B18" s="41" t="s">
+        <v>205</v>
+      </c>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="36">
+        <v>12</v>
+      </c>
+      <c r="B19" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="36">
+        <v>13</v>
+      </c>
+      <c r="B20" s="41" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="36">
+        <v>14</v>
+      </c>
+      <c r="B21" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="36">
+        <v>15</v>
+      </c>
+      <c r="B22" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="36">
+        <v>16</v>
+      </c>
+      <c r="B23" s="41" t="s">
+        <v>210</v>
+      </c>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="36">
+        <v>17</v>
+      </c>
+      <c r="B24" s="41" t="s">
+        <v>211</v>
+      </c>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="36">
+        <v>18</v>
+      </c>
+      <c r="B25" s="41" t="s">
+        <v>212</v>
+      </c>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="B27" s="42"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="B29" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="C29" s="21"/>
+      <c r="D29" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="36" t="s">
+        <v>222</v>
+      </c>
+      <c r="B30" s="43" t="s">
+        <v>223</v>
+      </c>
+      <c r="C30" s="21"/>
+      <c r="D30" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="36" t="s">
+        <v>225</v>
+      </c>
+      <c r="B31" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="C31" s="21"/>
+      <c r="D31" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="B32" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="C32" s="21"/>
+      <c r="D32" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="B33" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="C33" s="21"/>
+      <c r="D33" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="B34" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="C34" s="21"/>
+      <c r="D34" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="B35" s="43" t="s">
+        <v>237</v>
+      </c>
+      <c r="C35" s="21"/>
+      <c r="D35" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="36" t="s">
+        <v>239</v>
+      </c>
+      <c r="B36" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="C36" s="21"/>
+      <c r="D36" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="B37" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="C37" s="21"/>
+      <c r="D37" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="36" t="s">
+        <v>245</v>
+      </c>
+      <c r="B38" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="C38" s="21"/>
+      <c r="D38" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="36">
+        <v>11</v>
+      </c>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="36">
+        <v>12</v>
+      </c>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="36">
+        <v>13</v>
+      </c>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="36">
+        <v>14</v>
+      </c>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="36">
+        <v>15</v>
+      </c>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="B45" s="33"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="33"/>
+      <c r="E45" s="33"/>
+      <c r="F45" s="33"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="44"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="44"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="44"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="44"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="44"/>
+      <c r="F47" s="44"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="44"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="44"/>
+      <c r="F48" s="44"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A46:F48"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" sqref="C10:C25">
+      <formula1>"✅ OK,⚠️ Issue,❌ Problem,N/A"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C8:C25">
+      <formula1>"✅ OK,⚠️ Issue,❌ Problem,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
 </file>
--- a/public/downloads/estimate-slab-d9b2e5.xlsx
+++ b/public/downloads/estimate-slab-d9b2e5.xlsx
@@ -6,13 +6,39 @@
   <sheets>
     <sheet sheetId="1" name="📋 How to Use" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Estimate" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="✅ Site Conditions" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Change Order" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B63" authorId="0">
+      <text>
+        <r>
+          <t>Enter your overhead percentage (e.g. 10%, 12%, 15%). This covers insurance, office, vehicle, phone, etc.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B64" authorId="0">
+      <text>
+        <r>
+          <t>Enter your desired profit margin. 15-25% is typical for residential. 20-30% for decorative/specialty work.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="210">
   <si>
     <t>📋 HOW TO USE: Concrete Slab Estimate</t>
   </si>
@@ -71,7 +97,7 @@
     <t>8.</t>
   </si>
   <si>
-    <t>Set overhead % and profit margin % using dropdowns</t>
+    <t>Set overhead % and profit margin % in the yellow cells (type any value)</t>
   </si>
   <si>
     <t>9.</t>
@@ -83,9 +109,63 @@
     <t>10.</t>
   </si>
   <si>
+    <t>Use the Change Order sheet for any mid-project scope changes</t>
+  </si>
+  <si>
+    <t>11.</t>
+  </si>
+  <si>
     <t>Print or save as PDF for client presentation</t>
   </si>
   <si>
+    <t>12.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>13.</t>
+  </si>
+  <si>
+    <t>💡 SLAB PRO TIPS:</t>
+  </si>
+  <si>
+    <t>14.</t>
+  </si>
+  <si>
+    <t>• Always include vapor barrier under enclosed slabs — moisture wicking ruins floors</t>
+  </si>
+  <si>
+    <t>15.</t>
+  </si>
+  <si>
+    <t>• For garage slabs, use 4500 PSI concrete instead of 4000 for better durability</t>
+  </si>
+  <si>
+    <t>16.</t>
+  </si>
+  <si>
+    <t>• Place control joints every 8-12 feet (slab thickness in inches × 2.5 = max joint spacing in feet)</t>
+  </si>
+  <si>
+    <t>17.</t>
+  </si>
+  <si>
+    <t>• If the slab will support heavy equipment, upgrade to 6" with #4 rebar on 18" centers</t>
+  </si>
+  <si>
+    <t>18.</t>
+  </si>
+  <si>
+    <t>• Account for thickened edges if the slab will have walls built on it</t>
+  </si>
+  <si>
+    <t>19.</t>
+  </si>
+  <si>
+    <t>• Consider a 1-2% slope toward a floor drain for shops/garages</t>
+  </si>
+  <si>
     <t>🟡 YELLOW CELLS = Editable (enter your data here)</t>
   </si>
   <si>
@@ -425,9 +505,6 @@
     <t>Add/Remove</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Cost Impact</t>
   </si>
   <si>
@@ -492,6 +569,105 @@
   </si>
   <si>
     <t>Template from EstimateConcrete.com — Free concrete contractor tools</t>
+  </si>
+  <si>
+    <t>✅ SITE CONDITIONS CHECKLIST</t>
+  </si>
+  <si>
+    <t>Complete this checklist during your site visit. Fill in yellow cells.</t>
+  </si>
+  <si>
+    <t>Inspector:</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Site Condition</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Notes / Details</t>
+  </si>
+  <si>
+    <t>Access width for concrete truck (min 10')</t>
+  </si>
+  <si>
+    <t>Existing slab removal needed (Y/N)</t>
+  </si>
+  <si>
+    <t>Soil bearing capacity (compaction test done?)</t>
+  </si>
+  <si>
+    <t>Water table depth</t>
+  </si>
+  <si>
+    <t>Slope of site — fill needed?</t>
+  </si>
+  <si>
+    <t>Underground utilities marked</t>
+  </si>
+  <si>
+    <t>Intended use (garage, shop, storage, equipment)</t>
+  </si>
+  <si>
+    <t>Future wall or building placement on slab</t>
+  </si>
+  <si>
+    <t>ADDITIONAL OBSERVATIONS</t>
+  </si>
+  <si>
+    <t>SITE PHOTOS NEEDED</t>
+  </si>
+  <si>
+    <t>Overall site (wide angle)</t>
+  </si>
+  <si>
+    <t>Access point for concrete truck</t>
+  </si>
+  <si>
+    <t>Existing surface condition</t>
+  </si>
+  <si>
+    <t>Drainage/slope direction</t>
+  </si>
+  <si>
+    <t>Utility locations</t>
+  </si>
+  <si>
+    <t>Adjacent structures</t>
+  </si>
+  <si>
+    <t>CHANGE ORDER LOG</t>
+  </si>
+  <si>
+    <t>Track all mid-project scope changes. Get client approval before proceeding with any change.</t>
+  </si>
+  <si>
+    <t>Project:</t>
+  </si>
+  <si>
+    <t>Original Contract:</t>
+  </si>
+  <si>
+    <t>Description of Change</t>
+  </si>
+  <si>
+    <t>Added Cost</t>
+  </si>
+  <si>
+    <t>Client Approval Date</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>TOTAL CHANGE ORDERS</t>
+  </si>
+  <si>
+    <t>Revised Contract Total:</t>
   </si>
 </sst>
 </file>
@@ -501,7 +677,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -591,6 +767,16 @@
       <color rgb="FF94A3B8"/>
       <sz val="8"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF10B981"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -647,7 +833,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -692,6 +878,13 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1034,7 +1227,7 @@
   <sheetPr>
     <tabColor rgb="FFFEF3C7"/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1145,77 +1338,149 @@
         <v>23</v>
       </c>
     </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="5"/>
+      <c r="A18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="6"/>
+      <c r="A19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="7"/>
+      <c r="A20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="2"/>
+      <c r="A22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="8"/>
+      <c r="A23" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="8"/>
+      <c r="A24" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="8"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="8"/>
+      <c r="A25" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="8"/>
+      <c r="A27" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="5"/>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="8"/>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="9"/>
+      <c r="A28" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="6"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="7"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="10"/>
+      <c r="A31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="2"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="8"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="8"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="8"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="8"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" s="8"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="8"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="9"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -1223,18 +1488,18 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1256,7 +1521,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1266,7 +1531,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -1276,7 +1541,7 @@
     </row>
     <row r="3" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1286,98 +1551,98 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="B14" s="20">
         <v>12</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D14" s="21">
         <v>150</v>
@@ -1388,13 +1653,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B15" s="20">
         <v>8</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D15" s="21">
         <v>35</v>
@@ -1405,13 +1670,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B16" s="20">
         <v>1200</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D16" s="21">
         <v>0.15</v>
@@ -1422,13 +1687,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="B17" s="20">
         <v>400</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D17" s="21">
         <v>0.75</v>
@@ -1439,13 +1704,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="B18" s="20">
         <v>1200</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="D18" s="21">
         <v>0.45</v>
@@ -1456,13 +1721,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B19" s="20">
         <v>120</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D19" s="21">
         <v>1.25</v>
@@ -1473,13 +1738,13 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="B20" s="20">
         <v>5</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="D20" s="21">
         <v>18</v>
@@ -1490,13 +1755,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="B21" s="20">
         <v>1</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D21" s="21">
         <v>350</v>
@@ -1507,7 +1772,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -1518,37 +1783,37 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C25" s="18"/>
       <c r="D25" s="18" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="B26" s="20">
         <v>16</v>
@@ -1563,7 +1828,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="B27" s="20">
         <v>12</v>
@@ -1578,7 +1843,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="B28" s="20">
         <v>8</v>
@@ -1593,7 +1858,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="B29" s="20">
         <v>4</v>
@@ -1608,7 +1873,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="B30" s="20">
         <v>8</v>
@@ -1623,7 +1888,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="B31" s="20">
         <v>16</v>
@@ -1638,7 +1903,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B32" s="20">
         <v>4</v>
@@ -1653,7 +1918,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="B33" s="20">
         <v>6</v>
@@ -1668,7 +1933,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
@@ -1679,47 +1944,47 @@
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="18" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B38" s="20">
         <v>1</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="D38" s="21">
         <v>350</v>
@@ -1730,13 +1995,13 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="B39" s="20">
         <v>1</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="D39" s="21">
         <v>125</v>
@@ -1747,13 +2012,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="B40" s="20">
         <v>1</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="D40" s="21">
         <v>85</v>
@@ -1764,13 +2029,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="B41" s="20">
         <v>1</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="D41" s="21">
         <v>150</v>
@@ -1781,13 +2046,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="B42" s="20">
         <v>1</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="D42" s="21">
         <v>125</v>
@@ -1798,13 +2063,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="B43" s="20">
         <v>1</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="D43" s="21">
         <v>250</v>
@@ -1815,7 +2080,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="18" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="B44" s="18"/>
       <c r="C44" s="18"/>
@@ -1826,7 +2091,7 @@
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -1835,7 +2100,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="B47" s="20"/>
       <c r="C47" s="19"/>
@@ -1846,7 +2111,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="B48" s="20"/>
       <c r="C48" s="19"/>
@@ -1857,7 +2122,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="B49" s="20"/>
       <c r="C49" s="19"/>
@@ -1868,7 +2133,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="B50" s="20"/>
       <c r="C50" s="19"/>
@@ -1879,7 +2144,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="B51" s="20"/>
       <c r="C51" s="19"/>
@@ -1890,7 +2155,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="B52" s="20"/>
       <c r="C52" s="19"/>
@@ -1901,7 +2166,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="B53" s="20"/>
       <c r="C53" s="19"/>
@@ -1912,7 +2177,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="B54" s="20"/>
       <c r="C54" s="19"/>
@@ -1923,7 +2188,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="18" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B55" s="18"/>
       <c r="C55" s="18"/>
@@ -1934,7 +2199,7 @@
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
@@ -1943,7 +2208,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="B58" s="19"/>
       <c r="C58" s="19"/>
@@ -1954,7 +2219,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="19" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="B59" s="19"/>
       <c r="C59" s="19"/>
@@ -1965,7 +2230,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="19" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
@@ -1976,7 +2241,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="19" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B61" s="19"/>
       <c r="C61" s="19"/>
@@ -1987,7 +2252,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="18" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
@@ -1998,7 +2263,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="24" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="B63" s="25">
         <v>0.1</v>
@@ -2011,7 +2276,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="24" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B64" s="25">
         <v>0.15</v>
@@ -2024,7 +2289,7 @@
     </row>
     <row r="65" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="B65" s="27"/>
       <c r="C65" s="27"/>
@@ -2035,7 +2300,7 @@
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="16" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="B67" s="17"/>
       <c r="C67" s="17"/>
@@ -2044,7 +2309,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="29" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="B68" s="20"/>
       <c r="C68" s="20"/>
@@ -2053,7 +2318,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="29" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="B69" s="20"/>
       <c r="C69" s="20"/>
@@ -2062,7 +2327,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
@@ -2071,7 +2336,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="29" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="B71" s="20"/>
       <c r="C71" s="20"/>
@@ -2080,7 +2345,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="29" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="B72" s="20"/>
       <c r="C72" s="20"/>
@@ -2089,7 +2354,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="29" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="B73" s="20"/>
       <c r="C73" s="20"/>
@@ -2098,7 +2363,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="29" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="B74" s="20"/>
       <c r="C74" s="20"/>
@@ -2107,7 +2372,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="29" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="B75" s="20"/>
       <c r="C75" s="20"/>
@@ -2116,7 +2381,7 @@
     </row>
     <row r="77" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="16" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="B77" s="17"/>
       <c r="C77" s="17"/>
@@ -2125,7 +2390,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="30" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="B78" s="30"/>
       <c r="C78" s="30"/>
@@ -2134,7 +2399,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="30" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="B79" s="30"/>
       <c r="C79" s="30"/>
@@ -2143,7 +2408,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="30" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="B80" s="30"/>
       <c r="C80" s="30"/>
@@ -2152,7 +2417,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="30" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="B81" s="30"/>
       <c r="C81" s="30"/>
@@ -2161,7 +2426,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="30" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B82" s="30"/>
       <c r="C82" s="30"/>
@@ -2170,7 +2435,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="30" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="B83" s="30"/>
       <c r="C83" s="30"/>
@@ -2179,7 +2444,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="30" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="B84" s="30"/>
       <c r="C84" s="30"/>
@@ -2188,7 +2453,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="30" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="B85" s="30"/>
       <c r="C85" s="30"/>
@@ -2197,7 +2462,7 @@
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="16" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="B87" s="17"/>
       <c r="C87" s="17"/>
@@ -2206,19 +2471,19 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="18" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="B88" s="18" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="D88" s="18" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="E88" s="18" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -2258,7 +2523,7 @@
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="16" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="B95" s="17"/>
       <c r="C95" s="17"/>
@@ -2267,7 +2532,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="31" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="B96" s="31"/>
       <c r="C96" s="31"/>
@@ -2276,7 +2541,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="31" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B97" s="31"/>
       <c r="C97" s="31"/>
@@ -2285,7 +2550,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="31" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="B98" s="31"/>
       <c r="C98" s="31"/>
@@ -2294,7 +2559,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="31" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="B99" s="31"/>
       <c r="C99" s="31"/>
@@ -2303,7 +2568,7 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="31" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="B100" s="31"/>
       <c r="C100" s="31"/>
@@ -2312,7 +2577,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="31" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="B101" s="31"/>
       <c r="C101" s="31"/>
@@ -2321,7 +2586,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="31" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="B102" s="31"/>
       <c r="C102" s="31"/>
@@ -2330,7 +2595,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="31" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="B103" s="31"/>
       <c r="C103" s="31"/>
@@ -2339,7 +2604,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="31" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="B104" s="31"/>
       <c r="C104" s="31"/>
@@ -2348,32 +2613,32 @@
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="32" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="13" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="B112"/>
       <c r="C112"/>
@@ -2382,7 +2647,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="B113"/>
       <c r="C113"/>
@@ -2391,17 +2656,17 @@
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="33" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -2437,17 +2702,532 @@
     <mergeCell ref="A112:E112"/>
     <mergeCell ref="A113:E113"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="B63">
-      <formula1>"8%,10%,12%,15%"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B64">
-      <formula1>"10%,15%,20%,25%,30%,35%"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>EstimateConcrete.com — Professional Concrete Estimating Tools</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFD1FAE5"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D3" s="15"/>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="34">
+        <v>1</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="34">
+        <v>2</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="34">
+        <v>3</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="34">
+        <v>4</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="34">
+        <v>5</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="34">
+        <v>6</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="34">
+        <v>7</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="34">
+        <v>8</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>191</v>
+      </c>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C23" s="20"/>
+      <c r="D23" s="19"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="D24" s="19"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="C25" s="20"/>
+      <c r="D25" s="19"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="C26" s="20"/>
+      <c r="D26" s="19"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="C27" s="20"/>
+      <c r="D27" s="19"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="C28" s="20"/>
+      <c r="D28" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A22:D22"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" sqref="C10:C13">
+      <formula1>"✓ OK,⚠ Issue,✗ Fail,N/A"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C23:C28">
+      <formula1>"✓ Taken,☐ Needed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C6:C13">
+      <formula1>"✓ OK,⚠ Issue,✗ Fail,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFFECACA"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="36" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="D3" s="36" t="s">
+        <v>203</v>
+      </c>
+      <c r="E3" s="37"/>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="34">
+        <v>1</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="34">
+        <v>2</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="34">
+        <v>3</v>
+      </c>
+      <c r="B8" s="20"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="34">
+        <v>4</v>
+      </c>
+      <c r="B9" s="20"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="34">
+        <v>5</v>
+      </c>
+      <c r="B10" s="20"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="34">
+        <v>6</v>
+      </c>
+      <c r="B11" s="20"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="34">
+        <v>7</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="34">
+        <v>8</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="34">
+        <v>9</v>
+      </c>
+      <c r="B14" s="20"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="34">
+        <v>10</v>
+      </c>
+      <c r="B15" s="20"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="34">
+        <v>11</v>
+      </c>
+      <c r="B16" s="20"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="34">
+        <v>12</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="34">
+        <v>13</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="34">
+        <v>14</v>
+      </c>
+      <c r="B19" s="20"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="34">
+        <v>15</v>
+      </c>
+      <c r="B20" s="20"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="C21" s="23">
+        <f>SUM(C6:C20)</f>
+      </c>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="32" t="s">
+        <v>209</v>
+      </c>
+      <c r="C23" s="38">
+        <f>E3+C21</f>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" sqref="F10:F20">
+      <formula1>"Pending,Approved,Rejected,Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F6:F20">
+      <formula1>"Pending,Approved,Rejected,Completed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
--- a/public/downloads/estimate-slab-d9b2e5.xlsx
+++ b/public/downloads/estimate-slab-d9b2e5.xlsx
@@ -6,7 +6,7 @@
   <sheets>
     <sheet sheetId="1" name="📋 How to Use" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Estimate" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="✅ Site Conditions" state="visible" r:id="rId6"/>
+    <sheet sheetId="3" name="📍 Site Conditions" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Change Order" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="257">
   <si>
     <t>📋 HOW TO USE: Concrete Slab Estimate</t>
   </si>
@@ -175,6 +175,24 @@
     <t>✏️ EDITABLE CELLS: Yellow cells: quantities, unit prices, hours, rates, client info, overhead %, profit %</t>
   </si>
   <si>
+    <t>💡 PRO TIPS — INSIDER KNOWLEDGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  💡 Always install vapor barrier under enclosed slabs — moisture wicking through concrete ruins future floor coatings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  💡 Control joints must be cut within 6-12 hours. Cut depth = 1/4 of slab thickness. Waiting too long = random cracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  💡 For garage slabs, pour 1-2" above the driveway apron — prevents water from flowing into the garage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  💡 If the client plans walls later, install anchor bolts DURING the pour. Coming back to drill and epoxy costs 3x more</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  💡 Thickened edges add only $2-3/LF but increase structural integrity dramatically — always recommend them</t>
+  </si>
+  <si>
     <t>TIPS FOR PRINTING / PDF EXPORT</t>
   </si>
   <si>
@@ -571,19 +589,22 @@
     <t>Template from EstimateConcrete.com — Free concrete contractor tools</t>
   </si>
   <si>
-    <t>✅ SITE CONDITIONS CHECKLIST</t>
-  </si>
-  <si>
-    <t>Complete this checklist during your site visit. Fill in yellow cells.</t>
-  </si>
-  <si>
-    <t>Inspector:</t>
+    <t>📍 SITE CONDITIONS ASSESSMENT</t>
+  </si>
+  <si>
+    <t>Complete during site visit. Accurate assessment prevents costly surprises on pour day.</t>
+  </si>
+  <si>
+    <t>Site Visit Date:</t>
+  </si>
+  <si>
+    <t>Assessed By:</t>
   </si>
   <si>
     <t>#</t>
   </si>
   <si>
-    <t>Site Condition</t>
+    <t>Condition / Check Item</t>
   </si>
   <si>
     <t>Status</t>
@@ -592,6 +613,42 @@
     <t>Notes / Details</t>
   </si>
   <si>
+    <t>Photo Ref #</t>
+  </si>
+  <si>
+    <t>Action Needed</t>
+  </si>
+  <si>
+    <t>Truck access width (min 10' wide, 13' overhead)</t>
+  </si>
+  <si>
+    <t>Ground conditions — can trucks drive on site?</t>
+  </si>
+  <si>
+    <t>Underground utilities located and marked (call 811)</t>
+  </si>
+  <si>
+    <t>Water source available on site</t>
+  </si>
+  <si>
+    <t>Existing structures/surfaces to protect</t>
+  </si>
+  <si>
+    <t>Drainage pattern — where does water flow?</t>
+  </si>
+  <si>
+    <t>Soil type (clay / sand / rock / fill)</t>
+  </si>
+  <si>
+    <t>Grade / slope measurements taken</t>
+  </si>
+  <si>
+    <t>Property line / setback distances confirmed</t>
+  </si>
+  <si>
+    <t>Permits required (check local code office)</t>
+  </si>
+  <si>
     <t>Access width for concrete truck (min 10')</t>
   </si>
   <si>
@@ -616,28 +673,115 @@
     <t>Future wall or building placement on slab</t>
   </si>
   <si>
-    <t>ADDITIONAL OBSERVATIONS</t>
-  </si>
-  <si>
-    <t>SITE PHOTOS NEEDED</t>
-  </si>
-  <si>
-    <t>Overall site (wide angle)</t>
-  </si>
-  <si>
-    <t>Access point for concrete truck</t>
-  </si>
-  <si>
-    <t>Existing surface condition</t>
-  </si>
-  <si>
-    <t>Drainage/slope direction</t>
+    <t>📸 SITE PHOTO LOG</t>
+  </si>
+  <si>
+    <t>Photo #</t>
+  </si>
+  <si>
+    <t>Description / Location</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>File Name</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Overall site — wide angle</t>
+  </si>
+  <si>
+    <t>Before condition</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Truck access point</t>
+  </si>
+  <si>
+    <t>Access verification</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Work area — existing surface</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Drainage / water flow</t>
+  </si>
+  <si>
+    <t>Drainage planning</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Adjacent structures</t>
+  </si>
+  <si>
+    <t>Protection planning</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Utility markings</t>
   </si>
   <si>
     <t>Utility locations</t>
   </si>
   <si>
-    <t>Adjacent structures</t>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Soil condition</t>
+  </si>
+  <si>
+    <t>Soil assessment</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Grade / slope</t>
+  </si>
+  <si>
+    <t>Grading reference</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Property boundaries</t>
+  </si>
+  <si>
+    <t>Permit reference</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Obstacles / challenges</t>
+  </si>
+  <si>
+    <t>Planning</t>
+  </si>
+  <si>
+    <t>OVERALL SITE ASSESSMENT:</t>
   </si>
   <si>
     <t>CHANGE ORDER LOG</t>
@@ -659,9 +803,6 @@
   </si>
   <si>
     <t>Client Approval Date</t>
-  </si>
-  <si>
-    <t>Notes</t>
   </si>
   <si>
     <t>TOTAL CHANGE ORDERS</t>
@@ -768,9 +909,9 @@
       <sz val="8"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF1E293B"/>
-      <sz val="11"/>
+      <i/>
+      <color rgb="FF94A3B8"/>
+      <sz val="10"/>
     </font>
     <font>
       <b/>
@@ -778,7 +919,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -788,6 +929,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -833,7 +979,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -846,6 +992,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -856,33 +1003,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -1227,7 +1381,7 @@
   <sheetPr>
     <tabColor rgb="FFFEF3C7"/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1429,46 +1583,46 @@
       <c r="B29" s="7"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B31" s="2"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
+      <c r="B31" s="8"/>
+    </row>
+    <row r="32" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B32" s="8"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
+      <c r="B32" s="3"/>
+    </row>
+    <row r="33" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="8"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
+      <c r="B33" s="3"/>
+    </row>
+    <row r="34" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B34" s="8"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="8" t="s">
+      <c r="B34" s="3"/>
+    </row>
+    <row r="35" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="8"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
+      <c r="B35" s="3"/>
+    </row>
+    <row r="36" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="8"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
+      <c r="B36" s="3"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B37" s="8"/>
+      <c r="B38" s="2"/>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
@@ -1477,13 +1631,49 @@
       <c r="B39" s="9"/>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="10"/>
+      <c r="B40" s="9"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="9"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="9"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="9"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="9"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" s="10"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="22">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
@@ -1497,9 +1687,15 @@
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1520,1125 +1716,1125 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="A1" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+    </row>
+    <row r="3" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="21">
+        <v>12</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="22">
+        <v>150</v>
+      </c>
+      <c r="E14" s="23">
+        <f>B14*D14</f>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="21">
+        <v>8</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="22">
+        <v>35</v>
+      </c>
+      <c r="E15" s="23">
+        <f>B15*D15</f>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="21">
+        <v>1200</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" s="22">
+        <v>0.15</v>
+      </c>
+      <c r="E16" s="23">
+        <f>B16*D16</f>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="21">
+        <v>400</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="22">
+        <v>0.75</v>
+      </c>
+      <c r="E17" s="23">
+        <f>B17*D17</f>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="21">
+        <v>1200</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="22">
+        <v>0.45</v>
+      </c>
+      <c r="E18" s="23">
+        <f>B18*D18</f>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="21">
+        <v>120</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="22">
+        <v>1.25</v>
+      </c>
+      <c r="E19" s="23">
+        <f>B19*D19</f>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="21">
+        <v>5</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="22">
+        <v>18</v>
+      </c>
+      <c r="E20" s="23">
+        <f>B20*D20</f>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="21">
+        <v>1</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="22">
+        <v>350</v>
+      </c>
+      <c r="E21" s="23">
+        <f>B21*D21</f>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="24">
+        <f>SUM(E14:E21)</f>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B26" s="21">
+        <v>16</v>
+      </c>
+      <c r="C26" s="20"/>
+      <c r="D26" s="22">
         <v>55</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-    </row>
-    <row r="3" ht="25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="15" t="s">
+      <c r="E26" s="23">
+        <f>B26*D26</f>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" s="21">
+        <v>12</v>
+      </c>
+      <c r="C27" s="20"/>
+      <c r="D27" s="22">
+        <v>55</v>
+      </c>
+      <c r="E27" s="23">
+        <f>B27*D27</f>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" s="21">
+        <v>8</v>
+      </c>
+      <c r="C28" s="20"/>
+      <c r="D28" s="22">
+        <v>50</v>
+      </c>
+      <c r="E28" s="23">
+        <f>B28*D28</f>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B29" s="21">
+        <v>4</v>
+      </c>
+      <c r="C29" s="20"/>
+      <c r="D29" s="22">
+        <v>45</v>
+      </c>
+      <c r="E29" s="23">
+        <f>B29*D29</f>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30" s="21">
+        <v>8</v>
+      </c>
+      <c r="C30" s="20"/>
+      <c r="D30" s="22">
+        <v>55</v>
+      </c>
+      <c r="E30" s="23">
+        <f>B30*D30</f>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B31" s="21">
+        <v>16</v>
+      </c>
+      <c r="C31" s="20"/>
+      <c r="D31" s="22">
         <v>65</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="B14" s="20">
-        <v>12</v>
-      </c>
-      <c r="C14" s="19" t="s">
+      <c r="E31" s="23">
+        <f>B31*D31</f>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" s="21">
+        <v>4</v>
+      </c>
+      <c r="C32" s="20"/>
+      <c r="D32" s="22">
+        <v>55</v>
+      </c>
+      <c r="E32" s="23">
+        <f>B32*D32</f>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" s="21">
+        <v>6</v>
+      </c>
+      <c r="C33" s="20"/>
+      <c r="D33" s="22">
+        <v>45</v>
+      </c>
+      <c r="E33" s="23">
+        <f>B33*D33</f>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="24">
+        <f>SUM(E26:E33)</f>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="B36" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="21">
+      <c r="C36" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" s="21">
+        <v>1</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D38" s="22">
+        <v>350</v>
+      </c>
+      <c r="E38" s="23">
+        <f>B38*D38</f>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B39" s="21">
+        <v>1</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D39" s="22">
+        <v>125</v>
+      </c>
+      <c r="E39" s="23">
+        <f>B39*D39</f>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B40" s="21">
+        <v>1</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D40" s="22">
+        <v>85</v>
+      </c>
+      <c r="E40" s="23">
+        <f>B40*D40</f>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B41" s="21">
+        <v>1</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D41" s="22">
         <v>150</v>
       </c>
-      <c r="E14" s="22">
-        <f>B14*D14</f>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="20">
-        <v>8</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" s="21">
-        <v>35</v>
-      </c>
-      <c r="E15" s="22">
-        <f>B15*D15</f>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" s="20">
-        <v>1200</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" s="21">
+      <c r="E41" s="23">
+        <f>B41*D41</f>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B42" s="21">
+        <v>1</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D42" s="22">
+        <v>125</v>
+      </c>
+      <c r="E42" s="23">
+        <f>B42*D42</f>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B43" s="21">
+        <v>1</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="D43" s="22">
+        <v>250</v>
+      </c>
+      <c r="E43" s="23">
+        <f>B43*D43</f>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="24">
+        <f>SUM(E38:E43)</f>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B47" s="21"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="23">
+        <f>B47*D47</f>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="B48" s="21"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="23">
+        <f>B48*D48</f>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B49" s="21"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="23">
+        <f>B49*D49</f>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B50" s="21"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="23">
+        <f>B50*D50</f>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="B51" s="21"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="23">
+        <f>B51*D51</f>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" s="21"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="23">
+        <f>B52*D52</f>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="B53" s="21"/>
+      <c r="C53" s="20"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="23">
+        <f>B53*D53</f>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B54" s="21"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="23">
+        <f>B54*D54</f>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B55" s="19"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="24">
+        <f>SUM(E47:E54)</f>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="B58" s="20"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="23">
+        <f>E22</f>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B59" s="20"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="23">
+        <f>E34</f>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="B60" s="20"/>
+      <c r="C60" s="20"/>
+      <c r="D60" s="20"/>
+      <c r="E60" s="23">
+        <f>E44</f>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B61" s="20"/>
+      <c r="C61" s="20"/>
+      <c r="D61" s="20"/>
+      <c r="E61" s="23">
+        <f>E55</f>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B62" s="19"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="24">
+        <f>E58+E59+E60+E61</f>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="B63" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="C63" s="20"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="23">
+        <f>E62*B63</f>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B64" s="26">
         <v>0.15</v>
       </c>
-      <c r="E16" s="22">
-        <f>B16*D16</f>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="B17" s="20">
-        <v>400</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" s="21">
-        <v>0.75</v>
-      </c>
-      <c r="E17" s="22">
-        <f>B17*D17</f>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="B18" s="20">
-        <v>1200</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="21">
-        <v>0.45</v>
-      </c>
-      <c r="E18" s="22">
-        <f>B18*D18</f>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="B19" s="20">
-        <v>120</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="D19" s="21">
-        <v>1.25</v>
-      </c>
-      <c r="E19" s="22">
-        <f>B19*D19</f>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="B20" s="20">
-        <v>5</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" s="21">
-        <v>18</v>
-      </c>
-      <c r="E20" s="22">
-        <f>B20*D20</f>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="B21" s="20">
-        <v>1</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" s="21">
-        <v>350</v>
-      </c>
-      <c r="E21" s="22">
-        <f>B21*D21</f>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="23">
-        <f>SUM(E14:E21)</f>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="E25" s="18" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="B26" s="20">
-        <v>16</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="21">
-        <v>55</v>
-      </c>
-      <c r="E26" s="22">
-        <f>B26*D26</f>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="B27" s="20">
-        <v>12</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="21">
-        <v>55</v>
-      </c>
-      <c r="E27" s="22">
-        <f>B27*D27</f>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B28" s="20">
-        <v>8</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="21">
-        <v>50</v>
-      </c>
-      <c r="E28" s="22">
-        <f>B28*D28</f>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="B29" s="20">
-        <v>4</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="21">
-        <v>45</v>
-      </c>
-      <c r="E29" s="22">
-        <f>B29*D29</f>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="B30" s="20">
-        <v>8</v>
-      </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="21">
-        <v>55</v>
-      </c>
-      <c r="E30" s="22">
-        <f>B30*D30</f>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="B31" s="20">
-        <v>16</v>
-      </c>
-      <c r="C31" s="19"/>
-      <c r="D31" s="21">
-        <v>65</v>
-      </c>
-      <c r="E31" s="22">
-        <f>B31*D31</f>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B32" s="20">
-        <v>4</v>
-      </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="21">
-        <v>55</v>
-      </c>
-      <c r="E32" s="22">
-        <f>B32*D32</f>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="B33" s="20">
-        <v>6</v>
-      </c>
-      <c r="C33" s="19"/>
-      <c r="D33" s="21">
-        <v>45</v>
-      </c>
-      <c r="E33" s="22">
-        <f>B33*D33</f>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="23">
-        <f>SUM(E26:E33)</f>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="B38" s="20">
-        <v>1</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D38" s="21">
-        <v>350</v>
-      </c>
-      <c r="E38" s="22">
-        <f>B38*D38</f>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="20">
-        <v>1</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D39" s="21">
-        <v>125</v>
-      </c>
-      <c r="E39" s="22">
-        <f>B39*D39</f>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="B40" s="20">
-        <v>1</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D40" s="21">
-        <v>85</v>
-      </c>
-      <c r="E40" s="22">
-        <f>B40*D40</f>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="B41" s="20">
-        <v>1</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D41" s="21">
+      <c r="C64" s="20"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="23">
+        <f>(E62+E63)*B64</f>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="B65" s="28"/>
+      <c r="C65" s="28"/>
+      <c r="D65" s="28"/>
+      <c r="E65" s="29">
+        <f>E62+E63+E64</f>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="18"/>
+      <c r="E67" s="18"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="B68" s="21"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="B69" s="21"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="B70" s="21"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="B71" s="21"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="B72" s="21"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="B73" s="21"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="B74" s="21"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="B75" s="21"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="21"/>
+    </row>
+    <row r="77" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B77" s="18"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="18"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="E41" s="22">
-        <f>B41*D41</f>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="B42" s="20">
-        <v>1</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D42" s="21">
-        <v>125</v>
-      </c>
-      <c r="E42" s="22">
-        <f>B42*D42</f>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="B43" s="20">
-        <v>1</v>
-      </c>
-      <c r="C43" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="D43" s="21">
-        <v>250</v>
-      </c>
-      <c r="E43" s="22">
-        <f>B43*D43</f>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="B44" s="18"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="23">
-        <f>SUM(E38:E43)</f>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="B47" s="20"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="22">
-        <f>B47*D47</f>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="B48" s="20"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="22">
-        <f>B48*D48</f>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="B49" s="20"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="22">
-        <f>B49*D49</f>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="B50" s="20"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="22">
-        <f>B50*D50</f>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="B51" s="20"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="22">
-        <f>B51*D51</f>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="B52" s="20"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="22">
-        <f>B52*D52</f>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="B53" s="20"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="22">
-        <f>B53*D53</f>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="B54" s="20"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="22">
-        <f>B54*D54</f>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="23">
-        <f>SUM(E47:E54)</f>
-      </c>
-    </row>
-    <row r="57" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="22">
-        <f>E22</f>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="22">
-        <f>E34</f>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="22">
-        <f>E44</f>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="B61" s="19"/>
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="22">
-        <f>E55</f>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="B62" s="18"/>
-      <c r="C62" s="18"/>
-      <c r="D62" s="18"/>
-      <c r="E62" s="23">
-        <f>E58+E59+E60+E61</f>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="24" t="s">
-        <v>131</v>
-      </c>
-      <c r="B63" s="25">
-        <v>0.1</v>
-      </c>
-      <c r="C63" s="19"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="22">
-        <f>E62*B63</f>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="B64" s="25">
-        <v>0.15</v>
-      </c>
-      <c r="C64" s="19"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="22">
-        <f>(E62+E63)*B64</f>
-      </c>
-    </row>
-    <row r="65" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="B65" s="27"/>
-      <c r="C65" s="27"/>
-      <c r="D65" s="27"/>
-      <c r="E65" s="28">
-        <f>E62+E63+E64</f>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="B67" s="17"/>
-      <c r="C67" s="17"/>
-      <c r="D67" s="17"/>
-      <c r="E67" s="17"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="B68" s="20"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="20"/>
-      <c r="E68" s="20"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="B69" s="20"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="B71" s="20"/>
-      <c r="C71" s="20"/>
-      <c r="D71" s="20"/>
-      <c r="E71" s="20"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="B72" s="20"/>
-      <c r="C72" s="20"/>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="B73" s="20"/>
-      <c r="C73" s="20"/>
-      <c r="D73" s="20"/>
-      <c r="E73" s="20"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="B74" s="20"/>
-      <c r="C74" s="20"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-    </row>
-    <row r="77" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="B77" s="17"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="17"/>
-      <c r="E77" s="17"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="B78" s="30"/>
-      <c r="C78" s="30"/>
-      <c r="D78" s="30"/>
-      <c r="E78" s="30"/>
+      <c r="B78" s="31"/>
+      <c r="C78" s="31"/>
+      <c r="D78" s="31"/>
+      <c r="E78" s="31"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="30" t="s">
-        <v>145</v>
-      </c>
-      <c r="B79" s="30"/>
-      <c r="C79" s="30"/>
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
+      <c r="A79" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="B79" s="31"/>
+      <c r="C79" s="31"/>
+      <c r="D79" s="31"/>
+      <c r="E79" s="31"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="B80" s="30"/>
-      <c r="C80" s="30"/>
-      <c r="D80" s="30"/>
-      <c r="E80" s="30"/>
+      <c r="A80" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="B80" s="31"/>
+      <c r="C80" s="31"/>
+      <c r="D80" s="31"/>
+      <c r="E80" s="31"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="B81" s="30"/>
-      <c r="C81" s="30"/>
-      <c r="D81" s="30"/>
-      <c r="E81" s="30"/>
+      <c r="A81" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="B81" s="31"/>
+      <c r="C81" s="31"/>
+      <c r="D81" s="31"/>
+      <c r="E81" s="31"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="B82" s="30"/>
-      <c r="C82" s="30"/>
-      <c r="D82" s="30"/>
-      <c r="E82" s="30"/>
+      <c r="A82" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="B82" s="31"/>
+      <c r="C82" s="31"/>
+      <c r="D82" s="31"/>
+      <c r="E82" s="31"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="B83" s="30"/>
-      <c r="C83" s="30"/>
-      <c r="D83" s="30"/>
-      <c r="E83" s="30"/>
+      <c r="A83" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="B83" s="31"/>
+      <c r="C83" s="31"/>
+      <c r="D83" s="31"/>
+      <c r="E83" s="31"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="B84" s="30"/>
-      <c r="C84" s="30"/>
-      <c r="D84" s="30"/>
-      <c r="E84" s="30"/>
+      <c r="A84" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="B84" s="31"/>
+      <c r="C84" s="31"/>
+      <c r="D84" s="31"/>
+      <c r="E84" s="31"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="30" t="s">
-        <v>151</v>
-      </c>
-      <c r="B85" s="30"/>
-      <c r="C85" s="30"/>
-      <c r="D85" s="30"/>
-      <c r="E85" s="30"/>
+      <c r="A85" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="B85" s="31"/>
+      <c r="C85" s="31"/>
+      <c r="D85" s="31"/>
+      <c r="E85" s="31"/>
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="B87" s="17"/>
-      <c r="C87" s="17"/>
-      <c r="D87" s="17"/>
-      <c r="E87" s="17"/>
+      <c r="A87" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="B87" s="18"/>
+      <c r="C87" s="18"/>
+      <c r="D87" s="18"/>
+      <c r="E87" s="18"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="B88" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="C88" s="18" t="s">
+      <c r="A88" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B88" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C88" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D88" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="E88" s="18" t="s">
-        <v>156</v>
+      <c r="D88" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="E88" s="19" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="20"/>
-      <c r="B89" s="20"/>
-      <c r="C89" s="19"/>
-      <c r="D89" s="21"/>
-      <c r="E89" s="20"/>
+      <c r="A89" s="21"/>
+      <c r="B89" s="21"/>
+      <c r="C89" s="20"/>
+      <c r="D89" s="22"/>
+      <c r="E89" s="21"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="20"/>
-      <c r="B90" s="20"/>
-      <c r="C90" s="19"/>
-      <c r="D90" s="21"/>
-      <c r="E90" s="20"/>
+      <c r="A90" s="21"/>
+      <c r="B90" s="21"/>
+      <c r="C90" s="20"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="21"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="20"/>
-      <c r="B91" s="20"/>
-      <c r="C91" s="19"/>
-      <c r="D91" s="21"/>
-      <c r="E91" s="20"/>
+      <c r="A91" s="21"/>
+      <c r="B91" s="21"/>
+      <c r="C91" s="20"/>
+      <c r="D91" s="22"/>
+      <c r="E91" s="21"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="20"/>
-      <c r="B92" s="20"/>
-      <c r="C92" s="19"/>
-      <c r="D92" s="21"/>
-      <c r="E92" s="20"/>
+      <c r="A92" s="21"/>
+      <c r="B92" s="21"/>
+      <c r="C92" s="20"/>
+      <c r="D92" s="22"/>
+      <c r="E92" s="21"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="20"/>
-      <c r="B93" s="20"/>
-      <c r="C93" s="19"/>
-      <c r="D93" s="21"/>
-      <c r="E93" s="20"/>
+      <c r="A93" s="21"/>
+      <c r="B93" s="21"/>
+      <c r="C93" s="20"/>
+      <c r="D93" s="22"/>
+      <c r="E93" s="21"/>
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="B95" s="17"/>
-      <c r="C95" s="17"/>
-      <c r="D95" s="17"/>
-      <c r="E95" s="17"/>
+      <c r="A95" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="B95" s="18"/>
+      <c r="C95" s="18"/>
+      <c r="D95" s="18"/>
+      <c r="E95" s="18"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="B96" s="31"/>
-      <c r="C96" s="31"/>
-      <c r="D96" s="31"/>
-      <c r="E96" s="31"/>
+      <c r="A96" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="B96" s="32"/>
+      <c r="C96" s="32"/>
+      <c r="D96" s="32"/>
+      <c r="E96" s="32"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="B97" s="31"/>
-      <c r="C97" s="31"/>
-      <c r="D97" s="31"/>
-      <c r="E97" s="31"/>
+      <c r="A97" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="B97" s="32"/>
+      <c r="C97" s="32"/>
+      <c r="D97" s="32"/>
+      <c r="E97" s="32"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="B98" s="31"/>
-      <c r="C98" s="31"/>
-      <c r="D98" s="31"/>
-      <c r="E98" s="31"/>
+      <c r="A98" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="B98" s="32"/>
+      <c r="C98" s="32"/>
+      <c r="D98" s="32"/>
+      <c r="E98" s="32"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="B99" s="31"/>
-      <c r="C99" s="31"/>
-      <c r="D99" s="31"/>
-      <c r="E99" s="31"/>
+      <c r="A99" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="B99" s="32"/>
+      <c r="C99" s="32"/>
+      <c r="D99" s="32"/>
+      <c r="E99" s="32"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="B100" s="31"/>
-      <c r="C100" s="31"/>
-      <c r="D100" s="31"/>
-      <c r="E100" s="31"/>
+      <c r="A100" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="B100" s="32"/>
+      <c r="C100" s="32"/>
+      <c r="D100" s="32"/>
+      <c r="E100" s="32"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="B101" s="31"/>
-      <c r="C101" s="31"/>
-      <c r="D101" s="31"/>
-      <c r="E101" s="31"/>
+      <c r="A101" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="B101" s="32"/>
+      <c r="C101" s="32"/>
+      <c r="D101" s="32"/>
+      <c r="E101" s="32"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="B102" s="31"/>
-      <c r="C102" s="31"/>
-      <c r="D102" s="31"/>
-      <c r="E102" s="31"/>
+      <c r="A102" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="B102" s="32"/>
+      <c r="C102" s="32"/>
+      <c r="D102" s="32"/>
+      <c r="E102" s="32"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="B103" s="31"/>
-      <c r="C103" s="31"/>
-      <c r="D103" s="31"/>
-      <c r="E103" s="31"/>
+      <c r="A103" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="B103" s="32"/>
+      <c r="C103" s="32"/>
+      <c r="D103" s="32"/>
+      <c r="E103" s="32"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="31" t="s">
-        <v>166</v>
-      </c>
-      <c r="B104" s="31"/>
-      <c r="C104" s="31"/>
-      <c r="D104" s="31"/>
-      <c r="E104" s="31"/>
+      <c r="A104" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="B104" s="32"/>
+      <c r="C104" s="32"/>
+      <c r="D104" s="32"/>
+      <c r="E104" s="32"/>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="32" t="s">
-        <v>167</v>
+      <c r="A106" s="33" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="13" t="s">
-        <v>171</v>
+      <c r="A111" s="14" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B112"/>
       <c r="C112"/>
@@ -2647,7 +2843,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B113"/>
       <c r="C113"/>
@@ -2656,17 +2852,17 @@
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="33" t="s">
-        <v>176</v>
+      <c r="A118" s="34" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -2713,268 +2909,566 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FFD1FAE5"/>
+    <tabColor rgb="FF3B82F6"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="D3" s="15"/>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="34">
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="21"/>
+      <c r="C5" s="35" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" s="21"/>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="36">
         <v>1</v>
       </c>
-      <c r="B6" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="34">
+      <c r="B8" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="36">
         <v>2</v>
       </c>
-      <c r="B7" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="34">
+      <c r="B9" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="36">
         <v>3</v>
       </c>
-      <c r="B8" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="34">
+      <c r="B10" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="36">
         <v>4</v>
       </c>
-      <c r="B9" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="34">
+      <c r="B11" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="36">
         <v>5</v>
       </c>
-      <c r="B10" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="34">
+      <c r="B12" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="36">
         <v>6</v>
       </c>
-      <c r="B11" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="34">
+      <c r="B13" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="36">
         <v>7</v>
       </c>
-      <c r="B12" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="34">
+      <c r="B14" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="36">
         <v>8</v>
       </c>
-      <c r="B13" s="29" t="s">
-        <v>191</v>
-      </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-    </row>
-    <row r="16" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="20"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-    </row>
-    <row r="17" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="20"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-    </row>
-    <row r="18" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="20"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-    </row>
-    <row r="19" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="20"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-    </row>
-    <row r="20" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="20"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="35" t="s">
-        <v>193</v>
-      </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="19"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="C24" s="20"/>
-      <c r="D24" s="19"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="19"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="34" t="s">
+      <c r="B15" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="36">
+        <v>9</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="36">
         <v>10</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="19"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="34" t="s">
+      <c r="B17" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="36">
+        <v>11</v>
+      </c>
+      <c r="B18" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="36">
         <v>12</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="C27" s="20"/>
-      <c r="D27" s="19"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="34" t="s">
+      <c r="B19" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="36">
+        <v>13</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="36">
         <v>14</v>
       </c>
+      <c r="B21" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="36">
+        <v>15</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="36">
+        <v>16</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="36">
+        <v>17</v>
+      </c>
+      <c r="B24" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="36">
+        <v>18</v>
+      </c>
+      <c r="B25" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="19" t="s">
+        <v>212</v>
+      </c>
       <c r="B28" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="C28" s="20"/>
-      <c r="D28" s="19"/>
+        <v>213</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="36" t="s">
+        <v>218</v>
+      </c>
+      <c r="B29" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="C29" s="21"/>
+      <c r="D29" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="B30" s="39" t="s">
+        <v>222</v>
+      </c>
+      <c r="C30" s="21"/>
+      <c r="D30" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>225</v>
+      </c>
+      <c r="C31" s="21"/>
+      <c r="D31" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="36" t="s">
+        <v>226</v>
+      </c>
+      <c r="B32" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="C32" s="21"/>
+      <c r="D32" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="B33" s="39" t="s">
+        <v>230</v>
+      </c>
+      <c r="C33" s="21"/>
+      <c r="D33" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="36" t="s">
+        <v>232</v>
+      </c>
+      <c r="B34" s="39" t="s">
+        <v>233</v>
+      </c>
+      <c r="C34" s="21"/>
+      <c r="D34" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="B35" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="C35" s="21"/>
+      <c r="D35" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="B36" s="39" t="s">
+        <v>239</v>
+      </c>
+      <c r="C36" s="21"/>
+      <c r="D36" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="36" t="s">
+        <v>241</v>
+      </c>
+      <c r="B37" s="39" t="s">
+        <v>242</v>
+      </c>
+      <c r="C37" s="21"/>
+      <c r="D37" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="B38" s="39" t="s">
+        <v>245</v>
+      </c>
+      <c r="C38" s="21"/>
+      <c r="D38" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="36">
+        <v>11</v>
+      </c>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="36">
+        <v>12</v>
+      </c>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="36">
+        <v>13</v>
+      </c>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="36">
+        <v>14</v>
+      </c>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="36">
+        <v>15</v>
+      </c>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="B45" s="33"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="33"/>
+      <c r="E45" s="33"/>
+      <c r="F45" s="33"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="40"/>
+      <c r="B46" s="40"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="40"/>
+      <c r="E46" s="40"/>
+      <c r="F46" s="40"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="40"/>
+      <c r="B47" s="40"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="40"/>
+      <c r="E47" s="40"/>
+      <c r="F47" s="40"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="40"/>
+      <c r="B48" s="40"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="40"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A22:D22"/>
+  <mergeCells count="6">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A46:F48"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="C10:C13">
-      <formula1>"✓ OK,⚠ Issue,✗ Fail,N/A"</formula1>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" sqref="C10:C25">
+      <formula1>"✅ OK,⚠️ Issue,❌ Problem,N/A"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C23:C28">
-      <formula1>"✓ Taken,☐ Needed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C6:C13">
-      <formula1>"✓ OK,⚠ Issue,✗ Fail,N/A"</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="C8:C25">
+      <formula1>"✅ OK,⚠️ Issue,❌ Problem,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -2996,222 +3490,222 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="A1" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
+      <c r="A2" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
-        <v>202</v>
-      </c>
-      <c r="B3" s="15"/>
-      <c r="D3" s="36" t="s">
-        <v>203</v>
-      </c>
-      <c r="E3" s="37"/>
+      <c r="A3" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="D3" s="35" t="s">
+        <v>251</v>
+      </c>
+      <c r="E3" s="41"/>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>206</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>182</v>
+      <c r="A5" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="34">
+      <c r="A6" s="36">
         <v>1</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="34">
+      <c r="A7" s="36">
         <v>2</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="34">
+      <c r="A8" s="36">
         <v>3</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="34">
+      <c r="A9" s="36">
         <v>4</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="34">
+      <c r="A10" s="36">
         <v>5</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="34">
+      <c r="A11" s="36">
         <v>6</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="34">
+      <c r="A12" s="36">
         <v>7</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="34">
+      <c r="A13" s="36">
         <v>8</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="34">
+      <c r="A14" s="36">
         <v>9</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="34">
+      <c r="A15" s="36">
         <v>10</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="34">
+      <c r="A16" s="36">
         <v>11</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="34">
+      <c r="A17" s="36">
         <v>12</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="34">
+      <c r="A18" s="36">
         <v>13</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="34">
+      <c r="A19" s="36">
         <v>14</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="34">
+      <c r="A20" s="36">
         <v>15</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="C21" s="23">
+      <c r="A21" s="19"/>
+      <c r="B21" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="C21" s="24">
         <f>SUM(C6:C20)</f>
       </c>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="C23" s="38">
+      <c r="B23" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="C23" s="42">
         <f>E3+C21</f>
       </c>
     </row>
